--- a/source_data/workbooks/Source_Data_Fig6.xlsx
+++ b/source_data/workbooks/Source_Data_Fig6.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="51">
   <si>
     <t>plot_order</t>
   </si>
@@ -106,10 +106,7 @@
     <t>NOVA</t>
   </si>
   <si>
-    <t>GPT-5.2-vision</t>
-  </si>
-  <si>
-    <t>TLAgent</t>
+    <t>TissueLab</t>
   </si>
   <si>
     <t>accuracy</t>
@@ -142,19 +139,37 @@
     <t>correlation</t>
   </si>
   <si>
+    <t>system_description</t>
+  </si>
+  <si>
     <t>Figure 6f</t>
   </si>
   <si>
-    <t>TLAgent-R1</t>
-  </si>
-  <si>
-    <t>TLAgent-R2</t>
-  </si>
-  <si>
-    <t>TLAgent-R1+2</t>
-  </si>
-  <si>
-    <t>TLAgent-R1+2+Reflector</t>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>+ Skill 1 (Overlay)</t>
+  </si>
+  <si>
+    <t>+ Skill 2 (LN Size)</t>
+  </si>
+  <si>
+    <t>+ Skill 1 &amp; 2</t>
+  </si>
+  <si>
+    <t>+ Skill 1&amp;2 + VLM</t>
+  </si>
+  <si>
+    <t>TissueLab-R1</t>
+  </si>
+  <si>
+    <t>TissueLab-R2</t>
+  </si>
+  <si>
+    <t>TissueLab-R1+2</t>
+  </si>
+  <si>
+    <t>TissueLab-R1+2+Reflector</t>
   </si>
 </sst>
 </file>
@@ -486,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -573,10 +588,10 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H2">
         <v>321</v>
@@ -626,10 +641,10 @@
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <v>321</v>
@@ -679,10 +694,10 @@
         <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H4">
         <v>321</v>
@@ -732,10 +747,10 @@
         <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5">
         <v>321</v>
@@ -785,10 +800,10 @@
         <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H6">
         <v>321</v>
@@ -838,10 +853,10 @@
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7">
         <v>321</v>
@@ -891,10 +906,10 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H8">
         <v>321</v>
@@ -944,10 +959,10 @@
         <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H9">
         <v>321</v>
@@ -997,10 +1012,10 @@
         <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H10">
         <v>321</v>
@@ -1050,10 +1065,10 @@
         <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H11">
         <v>321</v>
@@ -1068,74 +1083,21 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>0.8791</v>
+        <v>0.9346</v>
       </c>
       <c r="M11">
-        <v>0.0135</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>0.8449</v>
+        <v>0.9065</v>
       </c>
       <c r="O11">
-        <v>0.9115</v>
+        <v>0.9595</v>
       </c>
       <c r="P11">
-        <v>0.8252</v>
+        <v>0.8931</v>
       </c>
       <c r="Q11">
-        <v>0.9244</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12">
-        <v>321</v>
-      </c>
-      <c r="I12">
-        <v>22</v>
-      </c>
-      <c r="J12">
-        <v>321</v>
-      </c>
-      <c r="K12">
-        <v>5</v>
-      </c>
-      <c r="L12">
-        <v>0.9346</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0.9065</v>
-      </c>
-      <c r="O12">
-        <v>0.9595</v>
-      </c>
-      <c r="P12">
-        <v>0.8931</v>
-      </c>
-      <c r="Q12">
         <v>0.9668</v>
       </c>
     </row>
@@ -1146,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1221,7 +1183,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -1233,10 +1195,10 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
         <v>34</v>
-      </c>
-      <c r="G2" t="s">
-        <v>35</v>
       </c>
       <c r="H2">
         <v>321</v>
@@ -1274,7 +1236,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -1286,10 +1248,10 @@
         <v>21</v>
       </c>
       <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
         <v>34</v>
-      </c>
-      <c r="G3" t="s">
-        <v>35</v>
       </c>
       <c r="H3">
         <v>321</v>
@@ -1327,22 +1289,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
         <v>33</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>34</v>
-      </c>
-      <c r="G4" t="s">
-        <v>35</v>
       </c>
       <c r="H4">
         <v>321</v>
@@ -1380,7 +1342,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -1392,10 +1354,10 @@
         <v>23</v>
       </c>
       <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
         <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
       </c>
       <c r="H5">
         <v>321</v>
@@ -1433,7 +1395,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -1445,10 +1407,10 @@
         <v>24</v>
       </c>
       <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
         <v>34</v>
-      </c>
-      <c r="G6" t="s">
-        <v>35</v>
       </c>
       <c r="H6">
         <v>321</v>
@@ -1486,7 +1448,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -1498,10 +1460,10 @@
         <v>25</v>
       </c>
       <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
         <v>34</v>
-      </c>
-      <c r="G7" t="s">
-        <v>35</v>
       </c>
       <c r="H7">
         <v>321</v>
@@ -1539,7 +1501,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -1551,10 +1513,10 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" t="s">
         <v>34</v>
-      </c>
-      <c r="G8" t="s">
-        <v>35</v>
       </c>
       <c r="H8">
         <v>321</v>
@@ -1592,7 +1554,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -1604,10 +1566,10 @@
         <v>27</v>
       </c>
       <c r="F9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" t="s">
         <v>34</v>
-      </c>
-      <c r="G9" t="s">
-        <v>35</v>
       </c>
       <c r="H9">
         <v>321</v>
@@ -1645,7 +1607,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -1657,10 +1619,10 @@
         <v>28</v>
       </c>
       <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
         <v>34</v>
-      </c>
-      <c r="G10" t="s">
-        <v>35</v>
       </c>
       <c r="H10">
         <v>321</v>
@@ -1698,7 +1660,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -1710,11 +1672,11 @@
         <v>29</v>
       </c>
       <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
         <v>34</v>
       </c>
-      <c r="G11" t="s">
-        <v>35</v>
-      </c>
       <c r="H11">
         <v>321</v>
       </c>
@@ -1728,74 +1690,21 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>0.3644</v>
+        <v>0.8272</v>
       </c>
       <c r="M11">
-        <v>0.0682</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>0.204</v>
+        <v>0.7338</v>
       </c>
       <c r="O11">
-        <v>0.5125</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="P11">
-        <v>0.0643</v>
+        <v>0.6554</v>
       </c>
       <c r="Q11">
-        <v>0.5417</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12">
-        <v>321</v>
-      </c>
-      <c r="I12">
-        <v>22</v>
-      </c>
-      <c r="J12">
-        <v>321</v>
-      </c>
-      <c r="K12">
-        <v>5</v>
-      </c>
-      <c r="L12">
-        <v>0.8272</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0.7338</v>
-      </c>
-      <c r="O12">
-        <v>0.9046999999999999</v>
-      </c>
-      <c r="P12">
-        <v>0.6554</v>
-      </c>
-      <c r="Q12">
         <v>0.9177</v>
       </c>
     </row>
@@ -1806,7 +1715,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q56"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1880,7 +1789,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -1892,10 +1801,10 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H2">
         <v>321</v>
@@ -1918,7 +1827,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -1930,10 +1839,10 @@
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <v>321</v>
@@ -1956,7 +1865,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -1968,10 +1877,10 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H4">
         <v>321</v>
@@ -2009,7 +1918,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -2021,10 +1930,10 @@
         <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5">
         <v>321</v>
@@ -2062,7 +1971,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -2074,10 +1983,10 @@
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H6">
         <v>321</v>
@@ -2115,7 +2024,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -2127,10 +2036,10 @@
         <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7">
         <v>321</v>
@@ -2153,7 +2062,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -2165,10 +2074,10 @@
         <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H8">
         <v>321</v>
@@ -2191,7 +2100,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2203,10 +2112,10 @@
         <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H9">
         <v>321</v>
@@ -2244,7 +2153,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -2256,10 +2165,10 @@
         <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H10">
         <v>321</v>
@@ -2297,7 +2206,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -2309,10 +2218,10 @@
         <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H11">
         <v>321</v>
@@ -2350,22 +2259,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
         <v>36</v>
       </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" t="s">
-        <v>37</v>
-      </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H12">
         <v>321</v>
@@ -2388,7 +2297,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -2400,10 +2309,10 @@
         <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H13">
         <v>321</v>
@@ -2426,7 +2335,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
@@ -2438,10 +2347,10 @@
         <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H14">
         <v>321</v>
@@ -2479,7 +2388,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
@@ -2491,10 +2400,10 @@
         <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H15">
         <v>321</v>
@@ -2532,7 +2441,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
@@ -2544,10 +2453,10 @@
         <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H16">
         <v>321</v>
@@ -2585,7 +2494,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
@@ -2597,10 +2506,10 @@
         <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H17">
         <v>321</v>
@@ -2623,7 +2532,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
@@ -2635,10 +2544,10 @@
         <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H18">
         <v>321</v>
@@ -2661,7 +2570,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
@@ -2673,10 +2582,10 @@
         <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H19">
         <v>321</v>
@@ -2714,7 +2623,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
         <v>18</v>
@@ -2726,10 +2635,10 @@
         <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H20">
         <v>321</v>
@@ -2767,7 +2676,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
@@ -2779,10 +2688,10 @@
         <v>23</v>
       </c>
       <c r="F21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H21">
         <v>321</v>
@@ -2820,7 +2729,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
         <v>18</v>
@@ -2832,10 +2741,10 @@
         <v>24</v>
       </c>
       <c r="F22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H22">
         <v>321</v>
@@ -2858,7 +2767,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
         <v>18</v>
@@ -2870,10 +2779,10 @@
         <v>24</v>
       </c>
       <c r="F23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H23">
         <v>321</v>
@@ -2896,7 +2805,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
@@ -2908,10 +2817,10 @@
         <v>24</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H24">
         <v>321</v>
@@ -2949,7 +2858,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
         <v>18</v>
@@ -2961,10 +2870,10 @@
         <v>24</v>
       </c>
       <c r="F25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H25">
         <v>321</v>
@@ -3002,7 +2911,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
         <v>18</v>
@@ -3014,10 +2923,10 @@
         <v>24</v>
       </c>
       <c r="F26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H26">
         <v>321</v>
@@ -3055,7 +2964,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
         <v>18</v>
@@ -3067,10 +2976,10 @@
         <v>25</v>
       </c>
       <c r="F27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H27">
         <v>321</v>
@@ -3093,7 +3002,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
         <v>18</v>
@@ -3105,10 +3014,10 @@
         <v>25</v>
       </c>
       <c r="F28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H28">
         <v>321</v>
@@ -3131,7 +3040,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
         <v>18</v>
@@ -3143,10 +3052,10 @@
         <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H29">
         <v>321</v>
@@ -3184,7 +3093,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s">
         <v>18</v>
@@ -3196,10 +3105,10 @@
         <v>25</v>
       </c>
       <c r="F30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H30">
         <v>321</v>
@@ -3237,7 +3146,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
         <v>18</v>
@@ -3249,10 +3158,10 @@
         <v>25</v>
       </c>
       <c r="F31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H31">
         <v>321</v>
@@ -3290,7 +3199,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
@@ -3302,10 +3211,10 @@
         <v>26</v>
       </c>
       <c r="F32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H32">
         <v>321</v>
@@ -3328,7 +3237,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" t="s">
         <v>18</v>
@@ -3340,10 +3249,10 @@
         <v>26</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H33">
         <v>321</v>
@@ -3366,7 +3275,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" t="s">
         <v>18</v>
@@ -3378,10 +3287,10 @@
         <v>26</v>
       </c>
       <c r="F34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H34">
         <v>321</v>
@@ -3419,7 +3328,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
         <v>18</v>
@@ -3431,10 +3340,10 @@
         <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H35">
         <v>321</v>
@@ -3472,7 +3381,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
         <v>18</v>
@@ -3484,10 +3393,10 @@
         <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H36">
         <v>321</v>
@@ -3525,7 +3434,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
@@ -3537,10 +3446,10 @@
         <v>27</v>
       </c>
       <c r="F37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H37">
         <v>321</v>
@@ -3563,7 +3472,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
         <v>18</v>
@@ -3575,10 +3484,10 @@
         <v>27</v>
       </c>
       <c r="F38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H38">
         <v>321</v>
@@ -3601,7 +3510,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
@@ -3613,10 +3522,10 @@
         <v>27</v>
       </c>
       <c r="F39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H39">
         <v>321</v>
@@ -3654,7 +3563,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C40" t="s">
         <v>18</v>
@@ -3666,10 +3575,10 @@
         <v>27</v>
       </c>
       <c r="F40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H40">
         <v>321</v>
@@ -3707,7 +3616,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C41" t="s">
         <v>18</v>
@@ -3719,10 +3628,10 @@
         <v>27</v>
       </c>
       <c r="F41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H41">
         <v>321</v>
@@ -3760,7 +3669,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C42" t="s">
         <v>18</v>
@@ -3772,10 +3681,10 @@
         <v>28</v>
       </c>
       <c r="F42" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H42">
         <v>321</v>
@@ -3798,7 +3707,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
@@ -3810,10 +3719,10 @@
         <v>28</v>
       </c>
       <c r="F43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H43">
         <v>321</v>
@@ -3836,7 +3745,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
@@ -3848,10 +3757,10 @@
         <v>28</v>
       </c>
       <c r="F44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H44">
         <v>321</v>
@@ -3889,7 +3798,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
@@ -3901,10 +3810,10 @@
         <v>28</v>
       </c>
       <c r="F45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H45">
         <v>321</v>
@@ -3942,7 +3851,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C46" t="s">
         <v>18</v>
@@ -3954,10 +3863,10 @@
         <v>28</v>
       </c>
       <c r="F46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H46">
         <v>321</v>
@@ -3995,7 +3904,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C47" t="s">
         <v>18</v>
@@ -4007,10 +3916,10 @@
         <v>29</v>
       </c>
       <c r="F47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H47">
         <v>321</v>
@@ -4022,10 +3931,10 @@
         <v>5</v>
       </c>
       <c r="L47">
-        <v>0.879</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="M47">
-        <v>0.013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:17">
@@ -4033,7 +3942,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C48" t="s">
         <v>18</v>
@@ -4045,10 +3954,10 @@
         <v>29</v>
       </c>
       <c r="F48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H48">
         <v>321</v>
@@ -4060,10 +3969,10 @@
         <v>5</v>
       </c>
       <c r="L48">
-        <v>0.851</v>
+        <v>0.947</v>
       </c>
       <c r="M48">
-        <v>0.011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:17">
@@ -4071,7 +3980,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C49" t="s">
         <v>18</v>
@@ -4083,10 +3992,10 @@
         <v>29</v>
       </c>
       <c r="F49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H49">
         <v>321</v>
@@ -4101,22 +4010,22 @@
         <v>5</v>
       </c>
       <c r="L49">
-        <v>0.8645</v>
+        <v>0.9395</v>
       </c>
       <c r="M49">
-        <v>0.0121</v>
+        <v>0</v>
       </c>
       <c r="N49">
-        <v>0.8236</v>
+        <v>0.9139</v>
       </c>
       <c r="O49">
-        <v>0.9031</v>
+        <v>0.9633</v>
       </c>
       <c r="P49">
-        <v>0.7956</v>
+        <v>0.8989</v>
       </c>
       <c r="Q49">
-        <v>0.9217</v>
+        <v>0.9702</v>
       </c>
     </row>
     <row r="50" spans="1:17">
@@ -4124,7 +4033,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C50" t="s">
         <v>18</v>
@@ -4136,10 +4045,10 @@
         <v>29</v>
       </c>
       <c r="F50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H50">
         <v>321</v>
@@ -4154,22 +4063,22 @@
         <v>5</v>
       </c>
       <c r="L50">
-        <v>0.8791</v>
+        <v>0.9346</v>
       </c>
       <c r="M50">
-        <v>0.0135</v>
+        <v>0</v>
       </c>
       <c r="N50">
-        <v>0.8449</v>
+        <v>0.9065</v>
       </c>
       <c r="O50">
-        <v>0.9115</v>
+        <v>0.9595</v>
       </c>
       <c r="P50">
-        <v>0.8252</v>
+        <v>0.8931</v>
       </c>
       <c r="Q50">
-        <v>0.9244</v>
+        <v>0.9668</v>
       </c>
     </row>
     <row r="51" spans="1:17">
@@ -4177,7 +4086,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
@@ -4189,10 +4098,10 @@
         <v>29</v>
       </c>
       <c r="F51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H51">
         <v>321</v>
@@ -4207,256 +4116,21 @@
         <v>5</v>
       </c>
       <c r="L51">
-        <v>0.3644</v>
+        <v>0.8272</v>
       </c>
       <c r="M51">
-        <v>0.0682</v>
+        <v>0</v>
       </c>
       <c r="N51">
-        <v>0.204</v>
+        <v>0.7338</v>
       </c>
       <c r="O51">
-        <v>0.5125</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="P51">
-        <v>0.0643</v>
+        <v>0.6554</v>
       </c>
       <c r="Q51">
-        <v>0.5417</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="s">
-        <v>36</v>
-      </c>
-      <c r="C52" t="s">
-        <v>18</v>
-      </c>
-      <c r="D52" t="s">
-        <v>19</v>
-      </c>
-      <c r="E52" t="s">
-        <v>30</v>
-      </c>
-      <c r="F52" t="s">
-        <v>37</v>
-      </c>
-      <c r="G52" t="s">
-        <v>32</v>
-      </c>
-      <c r="H52">
-        <v>321</v>
-      </c>
-      <c r="I52">
-        <v>22</v>
-      </c>
-      <c r="K52">
-        <v>5</v>
-      </c>
-      <c r="L52">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="s">
-        <v>36</v>
-      </c>
-      <c r="C53" t="s">
-        <v>18</v>
-      </c>
-      <c r="D53" t="s">
-        <v>19</v>
-      </c>
-      <c r="E53" t="s">
-        <v>30</v>
-      </c>
-      <c r="F53" t="s">
-        <v>38</v>
-      </c>
-      <c r="G53" t="s">
-        <v>32</v>
-      </c>
-      <c r="H53">
-        <v>321</v>
-      </c>
-      <c r="I53">
-        <v>22</v>
-      </c>
-      <c r="K53">
-        <v>5</v>
-      </c>
-      <c r="L53">
-        <v>0.947</v>
-      </c>
-      <c r="M53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="s">
-        <v>36</v>
-      </c>
-      <c r="C54" t="s">
-        <v>18</v>
-      </c>
-      <c r="D54" t="s">
-        <v>19</v>
-      </c>
-      <c r="E54" t="s">
-        <v>30</v>
-      </c>
-      <c r="F54" t="s">
-        <v>39</v>
-      </c>
-      <c r="G54" t="s">
-        <v>32</v>
-      </c>
-      <c r="H54">
-        <v>321</v>
-      </c>
-      <c r="I54">
-        <v>22</v>
-      </c>
-      <c r="J54">
-        <v>321</v>
-      </c>
-      <c r="K54">
-        <v>5</v>
-      </c>
-      <c r="L54">
-        <v>0.9395</v>
-      </c>
-      <c r="M54">
-        <v>0</v>
-      </c>
-      <c r="N54">
-        <v>0.9139</v>
-      </c>
-      <c r="O54">
-        <v>0.9633</v>
-      </c>
-      <c r="P54">
-        <v>0.8989</v>
-      </c>
-      <c r="Q54">
-        <v>0.9702</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="s">
-        <v>36</v>
-      </c>
-      <c r="C55" t="s">
-        <v>18</v>
-      </c>
-      <c r="D55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E55" t="s">
-        <v>30</v>
-      </c>
-      <c r="F55" t="s">
-        <v>31</v>
-      </c>
-      <c r="G55" t="s">
-        <v>32</v>
-      </c>
-      <c r="H55">
-        <v>321</v>
-      </c>
-      <c r="I55">
-        <v>22</v>
-      </c>
-      <c r="J55">
-        <v>321</v>
-      </c>
-      <c r="K55">
-        <v>5</v>
-      </c>
-      <c r="L55">
-        <v>0.9346</v>
-      </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
-      <c r="N55">
-        <v>0.9065</v>
-      </c>
-      <c r="O55">
-        <v>0.9595</v>
-      </c>
-      <c r="P55">
-        <v>0.8931</v>
-      </c>
-      <c r="Q55">
-        <v>0.9668</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="s">
-        <v>36</v>
-      </c>
-      <c r="C56" t="s">
-        <v>18</v>
-      </c>
-      <c r="D56" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" t="s">
-        <v>30</v>
-      </c>
-      <c r="F56" t="s">
-        <v>40</v>
-      </c>
-      <c r="G56" t="s">
-        <v>35</v>
-      </c>
-      <c r="H56">
-        <v>321</v>
-      </c>
-      <c r="I56">
-        <v>22</v>
-      </c>
-      <c r="J56">
-        <v>321</v>
-      </c>
-      <c r="K56">
-        <v>5</v>
-      </c>
-      <c r="L56">
-        <v>0.8272</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
-      </c>
-      <c r="N56">
-        <v>0.7338</v>
-      </c>
-      <c r="O56">
-        <v>0.9046999999999999</v>
-      </c>
-      <c r="P56">
-        <v>0.6554</v>
-      </c>
-      <c r="Q56">
         <v>0.9177</v>
       </c>
     </row>
@@ -4467,14 +4141,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="3" width="38.7109375" customWidth="1"/>
     <col min="4" max="4" width="19.7109375" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
@@ -4482,9 +4156,10 @@
     <col min="11" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="15" width="14.7109375" customWidth="1"/>
     <col min="16" max="17" width="13.7109375" customWidth="1"/>
+    <col min="18" max="18" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4536,8 +4211,11 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4551,13 +4229,13 @@
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
         <v>34</v>
-      </c>
-      <c r="G2" t="s">
-        <v>35</v>
       </c>
       <c r="H2">
         <v>321</v>
@@ -4589,8 +4267,11 @@
       <c r="Q2">
         <v>0.9177</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4604,13 +4285,13 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
         <v>34</v>
-      </c>
-      <c r="G3" t="s">
-        <v>35</v>
       </c>
       <c r="H3">
         <v>321</v>
@@ -4642,8 +4323,11 @@
       <c r="Q3">
         <v>0.9234</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4657,13 +4341,13 @@
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
         <v>34</v>
-      </c>
-      <c r="G4" t="s">
-        <v>35</v>
       </c>
       <c r="H4">
         <v>321</v>
@@ -4695,8 +4379,11 @@
       <c r="Q4">
         <v>0.9419</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4710,13 +4397,13 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
         <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
       </c>
       <c r="H5">
         <v>321</v>
@@ -4748,8 +4435,11 @@
       <c r="Q5">
         <v>0.9429</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4763,13 +4453,13 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
         <v>34</v>
-      </c>
-      <c r="G6" t="s">
-        <v>35</v>
       </c>
       <c r="H6">
         <v>321</v>
@@ -4800,6 +4490,9 @@
       </c>
       <c r="Q6">
         <v>0.9807</v>
+      </c>
+      <c r="R6" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
